--- a/journal_analyzer/graphy/감사조서/graphy_mapping_list_26년.xlsx
+++ b/journal_analyzer/graphy/감사조서/graphy_mapping_list_26년.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-19298" yWindow="-98" windowWidth="19396" windowHeight="12196" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
@@ -16,7 +16,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="18">
+  <fonts count="17">
     <font>
       <name val="맑은 고딕"/>
       <family val="2"/>
@@ -101,12 +101,6 @@
       <name val="맑은 고딕"/>
       <charset val="129"/>
       <family val="3"/>
-      <color rgb="FF444746"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <family val="2"/>
       <color rgb="FF444746"/>
       <sz val="9"/>
     </font>
@@ -208,21 +202,21 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
@@ -633,8 +627,8 @@
     <col width="23.83203125" customWidth="1" style="15" min="7" max="7"/>
     <col width="14.4140625" customWidth="1" style="15" min="8" max="8"/>
     <col width="14.6640625" customWidth="1" style="15" min="9" max="9"/>
-    <col width="8.6640625" customWidth="1" style="6" min="10" max="10"/>
-    <col width="8.6640625" customWidth="1" style="6" min="11" max="16384"/>
+    <col width="8.6640625" customWidth="1" style="6" min="10" max="11"/>
+    <col width="8.6640625" customWidth="1" style="6" min="12" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="17" customHeight="1">
@@ -685,7 +679,11 @@
       </c>
     </row>
     <row r="2" ht="17" customHeight="1">
-      <c r="A2" s="5" t="n"/>
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>일반사항</t>
+        </is>
+      </c>
       <c r="B2" s="9" t="inlineStr">
         <is>
           <t>분석결과_graphy</t>
@@ -693,7 +691,7 @@
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
-          <t>계정별원장_잔액표</t>
+          <t>계정별_기말잔액(TB_TO_GL_TEST)</t>
         </is>
       </c>
       <c r="D2" s="8" t="inlineStr">
@@ -708,19 +706,23 @@
       </c>
       <c r="F2" s="11" t="inlineStr">
         <is>
-          <t>JET_A_TEST</t>
+          <t>TB_TO_GL_TEST</t>
         </is>
       </c>
       <c r="G2" s="11" t="inlineStr">
         <is>
-          <t>a3</t>
+          <t>RL</t>
         </is>
       </c>
       <c r="H2" s="12" t="n"/>
       <c r="I2" s="11" t="n"/>
     </row>
     <row r="3" ht="17" customHeight="1">
-      <c r="A3" s="5" t="n"/>
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>일반사항</t>
+        </is>
+      </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
           <t>분석결과_graphy</t>
@@ -755,7 +757,11 @@
       <c r="I3" s="11" t="n"/>
     </row>
     <row r="4" ht="17" customHeight="1">
-      <c r="A4" s="5" t="n"/>
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>일반사항</t>
+        </is>
+      </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
           <t>분석결과_graphy</t>
@@ -790,7 +796,11 @@
       <c r="I4" s="11" t="n"/>
     </row>
     <row r="5" ht="17" customHeight="1">
-      <c r="A5" s="5" t="n"/>
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>일반사항</t>
+        </is>
+      </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
           <t>분석결과_graphy</t>
@@ -825,7 +835,11 @@
       <c r="I5" s="11" t="n"/>
     </row>
     <row r="6" ht="17" customHeight="1">
-      <c r="A6" s="5" t="n"/>
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>일반사항</t>
+        </is>
+      </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
           <t>분석결과_graphy</t>
@@ -950,7 +964,7 @@
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>상대_외상매출금</t>
+          <t>상대_외상매출금_차변</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
@@ -1067,7 +1081,7 @@
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>상대_외상매입금</t>
+          <t>상대_외상매입금_대변</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
@@ -1496,7 +1510,7 @@
       </c>
       <c r="C23" s="13" t="inlineStr">
         <is>
-          <t>상대_국내제품매출액</t>
+          <t>상대_국내제품매출액_대변</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
@@ -1535,7 +1549,7 @@
       </c>
       <c r="C24" s="13" t="inlineStr">
         <is>
-          <t>상대_해외제품매출액</t>
+          <t>상대_해외제품매출액_대변</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
@@ -1574,7 +1588,7 @@
       </c>
       <c r="C25" s="13" t="inlineStr">
         <is>
-          <t>상대_국내상품매출액</t>
+          <t>상대_국내상품매출액_대변</t>
         </is>
       </c>
       <c r="D25" s="8" t="inlineStr">
@@ -1613,7 +1627,7 @@
       </c>
       <c r="C26" s="13" t="inlineStr">
         <is>
-          <t>상대_해외상품매출액</t>
+          <t>상대_해외상품매출액_대변</t>
         </is>
       </c>
       <c r="D26" s="8" t="inlineStr">
